--- a/data_hp.xlsx
+++ b/data_hp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lian Bhara\Downloads\Project MAP Lian\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB48F071-E18A-4109-BAED-7A1AD0BCC186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C6ABEB-84C3-4062-BAF1-D7D9A154BB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{34597623-C4F7-4849-982B-78321F808F8F}"/>
   </bookViews>
@@ -68,9 +68,6 @@
     <t>Samsung</t>
   </si>
   <si>
-    <t>Galaxy S25</t>
-  </si>
-  <si>
     <t>Flagship</t>
   </si>
   <si>
@@ -89,9 +86,6 @@
     <t>Xiaomi</t>
   </si>
   <si>
-    <t>17T Pro</t>
-  </si>
-  <si>
     <t>Kamera Leica 50MP</t>
   </si>
   <si>
@@ -107,9 +101,6 @@
     <t>iPhone</t>
   </si>
   <si>
-    <t>17e</t>
-  </si>
-  <si>
     <t>Chip A19</t>
   </si>
   <si>
@@ -122,9 +113,6 @@
     <t>Apple Fans</t>
   </si>
   <si>
-    <t>Galaxy A57 5G</t>
-  </si>
-  <si>
     <t>Mid-Range</t>
   </si>
   <si>
@@ -140,9 +128,6 @@
     <t>Pengguna Sehari-hari</t>
   </si>
   <si>
-    <t>17T</t>
-  </si>
-  <si>
     <t>Mid-High</t>
   </si>
   <si>
@@ -156,6 +141,21 @@
   </si>
   <si>
     <t>Gamer</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy S25</t>
+  </si>
+  <si>
+    <t>Xiaomi 17T Pro</t>
+  </si>
+  <si>
+    <t>Iphone 17e</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy A57 5G</t>
+  </si>
+  <si>
+    <t>Xiaomi 17T</t>
   </si>
 </sst>
 </file>
@@ -569,77 +569,77 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C2">
         <v>12999000</v>
       </c>
       <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C3">
         <v>12999000</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C4">
         <v>13499000</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
         <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -647,51 +647,51 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C5">
         <v>7599000</v>
       </c>
       <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
         <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C6">
         <v>9999000</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/data_hp.xlsx
+++ b/data_hp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lian Bhara\Downloads\Project MAP Lian\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C6ABEB-84C3-4062-BAF1-D7D9A154BB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF34C1A8-B7CE-41A1-BD59-8C0F8D04A34F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{34597623-C4F7-4849-982B-78321F808F8F}"/>
   </bookViews>
@@ -68,6 +68,9 @@
     <t>Samsung</t>
   </si>
   <si>
+    <t>Galaxy S25</t>
+  </si>
+  <si>
     <t>Flagship</t>
   </si>
   <si>
@@ -86,6 +89,9 @@
     <t>Xiaomi</t>
   </si>
   <si>
+    <t>17T Pro</t>
+  </si>
+  <si>
     <t>Kamera Leica 50MP</t>
   </si>
   <si>
@@ -101,6 +107,9 @@
     <t>iPhone</t>
   </si>
   <si>
+    <t>17e</t>
+  </si>
+  <si>
     <t>Chip A19</t>
   </si>
   <si>
@@ -113,6 +122,9 @@
     <t>Apple Fans</t>
   </si>
   <si>
+    <t>Galaxy A57 5G</t>
+  </si>
+  <si>
     <t>Mid-Range</t>
   </si>
   <si>
@@ -128,6 +140,9 @@
     <t>Pengguna Sehari-hari</t>
   </si>
   <si>
+    <t>17T</t>
+  </si>
+  <si>
     <t>Mid-High</t>
   </si>
   <si>
@@ -141,21 +156,6 @@
   </si>
   <si>
     <t>Gamer</t>
-  </si>
-  <si>
-    <t>Samsung Galaxy S25</t>
-  </si>
-  <si>
-    <t>Xiaomi 17T Pro</t>
-  </si>
-  <si>
-    <t>Iphone 17e</t>
-  </si>
-  <si>
-    <t>Samsung Galaxy A57 5G</t>
-  </si>
-  <si>
-    <t>Xiaomi 17T</t>
   </si>
 </sst>
 </file>
@@ -569,77 +569,77 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>12999000</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>12999000</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C4">
         <v>13499000</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -647,51 +647,51 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>7599000</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>9999000</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/data_hp.xlsx
+++ b/data_hp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lian Bhara\Downloads\Project MAP Lian\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF34C1A8-B7CE-41A1-BD59-8C0F8D04A34F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2347EE-5EA9-49D2-BCFC-BC64ECD1FDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{34597623-C4F7-4849-982B-78321F808F8F}"/>
   </bookViews>
@@ -74,15 +74,6 @@
     <t>Flagship</t>
   </si>
   <si>
-    <t>Chipset Snapdragon 8 Gen 4</t>
-  </si>
-  <si>
-    <t>Kamera 50MP</t>
-  </si>
-  <si>
-    <t>Layar 120Hz</t>
-  </si>
-  <si>
     <t>Profesional</t>
   </si>
   <si>
@@ -92,15 +83,6 @@
     <t>17T Pro</t>
   </si>
   <si>
-    <t>Kamera Leica 50MP</t>
-  </si>
-  <si>
-    <t>Charging 120W</t>
-  </si>
-  <si>
-    <t>Layar AMOLED</t>
-  </si>
-  <si>
     <t>Fotografer</t>
   </si>
   <si>
@@ -110,15 +92,6 @@
     <t>17e</t>
   </si>
   <si>
-    <t>Chip A19</t>
-  </si>
-  <si>
-    <t>Apple Intelligence</t>
-  </si>
-  <si>
-    <t>Ekosistem Apple</t>
-  </si>
-  <si>
     <t>Apple Fans</t>
   </si>
   <si>
@@ -128,15 +101,6 @@
     <t>Mid-Range</t>
   </si>
   <si>
-    <t>Baterai 5000 mAh</t>
-  </si>
-  <si>
-    <t>Kamera 50MP OIS</t>
-  </si>
-  <si>
-    <t>Update 6 Tahun</t>
-  </si>
-  <si>
     <t>Pengguna Sehari-hari</t>
   </si>
   <si>
@@ -146,16 +110,52 @@
     <t>Mid-High</t>
   </si>
   <si>
-    <t>Chipset Dimensity</t>
-  </si>
-  <si>
-    <t>Kamera 108MP</t>
-  </si>
-  <si>
-    <t>Charging Cepat</t>
-  </si>
-  <si>
     <t>Gamer</t>
+  </si>
+  <si>
+    <t>Satu-satunya HP kompak 6.2 inci dengan chipset Snapdragon 8 Elite for Galaxy — performa AI-nya 40% lebih kencang dari generasi sebelumnya</t>
+  </si>
+  <si>
+    <t>Flagship paling ringan di kelasnya — bobot cuma 162 gram dengan ketebalan 7,2mm, nyaman dipakai satu tangan</t>
+  </si>
+  <si>
+    <t>Galaxy AI dengan multimodal agent — bisa paham teks, suara, gambar, dan video sekaligus dalam satu perintah</t>
+  </si>
+  <si>
+    <t>Satu-satunya HP Rp12 jutaan dengan telefoto periskop Leica 5x optical zoom — bisa zoom sampai 120x AI Ultra Zoom dan foto makro dari jarak 30 cm.</t>
+  </si>
+  <si>
+    <t>Baterai 7000mAh dengan teknologi silicon-carbon — 100W wired charging + 50W wireless charging, tahan lebih dari 1 hari pemakaian normal.</t>
+  </si>
+  <si>
+    <t>Layar 6,83 inci 1.5K AMOLED 144Hz dengan puncak kecerahan 3500 nits — dilapisi Gorilla Glass 7i dan sertifikasi TÜV Rheinland untuk perlindungan mata.</t>
+  </si>
+  <si>
+    <t>Chip A19 3nm dengan CPU 6-core — performa hingga 2x lebih cepat dari iPhone 11, dan GPU 4-core dengan Neural Accelerators untuk grafis kelas konsol.</t>
+  </si>
+  <si>
+    <t>Kamera 48MP Fusion dengan optical-quality 2x Telephoto — bisa foto jarak jauh tanpa kehilangan detail, plus next-generation portraits yang otomatis mengenali manusia, anjing, dan kucing.</t>
+  </si>
+  <si>
+    <t>MagSafe 15W wireless charging + Ceramic Shield 2 dengan ketahanan gores 3x lebih baik dari generasi sebelumnya, plus lapisan anti-reflektif untuk mengurangi silau.</t>
+  </si>
+  <si>
+    <t>Smartphone tertipis di kelas mid-range — ketebalan hanya 6,9mm dengan bobot 179 gram, 7% lebih tipis dan 19 gram lebih ringan dari Galaxy A56 5G.</t>
+  </si>
+  <si>
+    <t>Pertama kali di seri Galaxy A dengan IP68 + Gorilla Glass Victus+ — tahan air hingga kedalaman 1,5 meter selama 30 menit, plus layar dan bodi belakang yang tahan gores.</t>
+  </si>
+  <si>
+    <t>Satu-satunya di kelasnya dengan 6x upgrade Android OS + 6 tahun security update — plus baterai 5.000mAh yang tahan 2 hari dan charging 45W.</t>
+  </si>
+  <si>
+    <t>Satu-satunya di kelasnya dengan telefoto periskop 50MP — 5x optical zoom, 10x lossless, 120x AI Ultra Zoom</t>
+  </si>
+  <si>
+    <t>Baterai 6500mAh silicon-carbon — terbesar di kelas upper-midrange, charging 67W</t>
+  </si>
+  <si>
+    <t>Layar 6,59" 1.5K AMOLED 120Hz, 3500 nits — tertinggi di kelasnya + Gorilla Glass 7i + IP68</t>
   </si>
 </sst>
 </file>
@@ -533,9 +533,10 @@
     <col min="2" max="2" width="14.5546875" customWidth="1"/>
     <col min="3" max="3" width="11.77734375" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="14.21875" customWidth="1"/>
+    <col min="5" max="5" width="35.88671875" customWidth="1"/>
+    <col min="6" max="6" width="36.5546875" customWidth="1"/>
+    <col min="7" max="7" width="30.6640625" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -578,24 +579,24 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s">
         <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>12999000</v>
@@ -604,24 +605,24 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C4">
         <v>13499000</v>
@@ -630,16 +631,16 @@
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -647,51 +648,51 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C5">
         <v>7599000</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>9999000</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/data_hp.xlsx
+++ b/data_hp.xlsx
@@ -8,12 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lian Bhara\Downloads\Project MAP Lian\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2347EE-5EA9-49D2-BCFC-BC64ECD1FDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA72B7CC-4610-4A1B-9AE0-E6CAE0E2BE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{34597623-C4F7-4849-982B-78321F808F8F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="7" xr2:uid="{34597623-C4F7-4849-982B-78321F808F8F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Samsung" sheetId="1" r:id="rId1"/>
+    <sheet name="Iphone" sheetId="2" r:id="rId2"/>
+    <sheet name="Xiaomi" sheetId="3" r:id="rId3"/>
+    <sheet name="Oppo" sheetId="4" r:id="rId4"/>
+    <sheet name="Motorola" sheetId="5" r:id="rId5"/>
+    <sheet name="Infinix" sheetId="6" r:id="rId6"/>
+    <sheet name="Huawei" sheetId="7" r:id="rId7"/>
+    <sheet name="Kompetitor" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="53">
   <si>
     <t>Brand</t>
   </si>
@@ -156,6 +163,48 @@
   </si>
   <si>
     <t>Layar 6,59" 1.5K AMOLED 120Hz, 3500 nits — tertinggi di kelasnya + Gorilla Glass 7i + IP68</t>
+  </si>
+  <si>
+    <t>Chipset</t>
+  </si>
+  <si>
+    <t>Dimensity 8500 Ultra</t>
+  </si>
+  <si>
+    <t>Dimensity 9500</t>
+  </si>
+  <si>
+    <t>Apple A19</t>
+  </si>
+  <si>
+    <t>Snapdragon 8 Elite</t>
+  </si>
+  <si>
+    <t>Exynos 1680</t>
+  </si>
+  <si>
+    <t>Baterai 8.340mAh silicon-carbon — terbesar di kelasnya, tahan 2-3 hari, charging 67W HyperCharge</t>
+  </si>
+  <si>
+    <t>Layar 6,83" 1.5K AMOLED 120Hz, 3.500 nits — tertinggi di kelasnya + Gorilla Glass Victus 2</t>
+  </si>
+  <si>
+    <t>Sertifikasi IP69K + tahan benturan — perlindungan air &amp; debu paling tangguh di kelas menengah</t>
+  </si>
+  <si>
+    <t>Snapdragon 6s Gen 4</t>
+  </si>
+  <si>
+    <t>Pengguna aktif, pekerja lapangan, content creator pemula</t>
+  </si>
+  <si>
+    <t>Redmi Note 17 Pro 5G</t>
+  </si>
+  <si>
+    <t>Poco</t>
+  </si>
+  <si>
+    <t>X8 5G</t>
   </si>
 </sst>
 </file>
@@ -527,19 +576,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{806A3B1B-30BD-46F4-967F-BAEB25735AE2}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.5546875" customWidth="1"/>
     <col min="3" max="3" width="11.77734375" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="35.88671875" customWidth="1"/>
-    <col min="6" max="6" width="36.5546875" customWidth="1"/>
-    <col min="7" max="7" width="30.6640625" customWidth="1"/>
-    <col min="8" max="8" width="21.44140625" customWidth="1"/>
+    <col min="5" max="5" width="18.21875" customWidth="1"/>
+    <col min="6" max="6" width="35.88671875" customWidth="1"/>
+    <col min="7" max="7" width="36.5546875" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -553,19 +603,22 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -579,120 +632,518 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" t="s">
         <v>24</v>
       </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>7599000</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF6D4B3D-10C7-4E8A-A722-1B8A27F4E87E}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="35.88671875" customWidth="1"/>
+    <col min="7" max="7" width="36.5546875" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2">
+        <v>13499000</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>42</v>
+      </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3156EC32-DC0B-4F51-BC7B-AF12F7A8DA01}">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="19.88671875" customWidth="1"/>
+    <col min="6" max="6" width="35.88671875" customWidth="1"/>
+    <col min="7" max="7" width="36.5546875" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>12999000</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C3">
-        <v>12999000</v>
+        <v>9999000</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="C4">
-        <v>13499000</v>
+        <v>5699000</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5">
-        <v>7599000</v>
-      </c>
-      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{346B3E3D-4E90-4F4D-9CC6-50E03842B365}">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="35.88671875" customWidth="1"/>
+    <col min="7" max="7" width="36.5546875" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC137A39-8C1C-43BF-8EA6-B0349BF79526}">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="35.88671875" customWidth="1"/>
+    <col min="7" max="7" width="36.5546875" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D5AFE1-9881-4B45-8BF9-A9C996CF07ED}">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="35.88671875" customWidth="1"/>
+    <col min="7" max="7" width="36.5546875" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{014DB7A5-C0FE-4878-9ACA-3B749580D0EC}">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="35.88671875" customWidth="1"/>
+    <col min="7" max="7" width="36.5546875" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB1CEFC5-5F0F-4437-842B-A0CCBC520DBE}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="35.88671875" customWidth="1"/>
+    <col min="7" max="7" width="36.5546875" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2">
+        <v>5640000</v>
+      </c>
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6">
-        <v>9999000</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" t="s">
-        <v>23</v>
+      <c r="E2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
